--- a/templates/BASE_SEMANAL_DADOS.xlsx
+++ b/templates/BASE_SEMANAL_DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trinuscapital-my.sharepoint.com/personal/mateus_monteiro_trinusco_com_br/Documents/Área de Trabalho/TEMPORARIO/SEMANAL - ENTREGA/Relatorios/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_C7687B5054A33544D9B01B6F03B42F07F57BE01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1109713E-4D9E-4149-B7FB-1DA1A02A32B6}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_C7687B5054A33544D9B01B6F03B42F07F57BE01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAD0218F-49AE-4DBF-B3D1-3F75F5289E19}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="345">
   <si>
     <t>CHECKLIST DE ÁREA COMUM</t>
   </si>
@@ -1403,14 +1403,21 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="44" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1434,13 +1441,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1448,9 +1448,6 @@
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="43">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1460,16 +1457,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom"/>
@@ -1575,11 +1562,20 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FFCBD5E1"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom"/>
@@ -1643,6 +1639,10 @@
           <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
@@ -1795,13 +1795,13 @@
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="UNIDADE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DATA VISTORIA" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DATA VISTORIA" dataDxfId="32"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="STATUS"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="MOTIVO REPROVAÇÃO"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="SEMANA Nº" dataDxfId="32">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="SEMANA Nº" dataDxfId="31">
       <calculatedColumnFormula>IF(B4="","",WEEKNUM(B4,1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MÊS" dataDxfId="31">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MÊS" dataDxfId="30">
       <calculatedColumnFormula>IF(B4="","",TEXT(B4,"mmmm"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1810,60 +1810,60 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela4" displayName="Tabela4" ref="A3:I13" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela4" displayName="Tabela4" ref="A3:I13" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A3:I13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="DATA CADASTRO" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="TIPO" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="DESCRIÇÃO" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="1º PRAZO" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="PRAZO ATUAL" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="DELTA DIAS" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="DATA CADASTRO" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="TIPO" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="DESCRIÇÃO" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="1º PRAZO" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="PRAZO ATUAL" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="DELTA DIAS" dataDxfId="21">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",E4-D4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="RESPONSÁVEL" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{6816C52C-219B-44C5-9460-FB46A53D1694}" name="OCULTAR" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="RESPONSÁVEL" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="STATUS" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{6816C52C-219B-44C5-9460-FB46A53D1694}" name="OCULTAR" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TAB - MATEUS MONTEIRO" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabela5" displayName="Tabela5" ref="A3:O29" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabela5" displayName="Tabela5" ref="A3:O29" totalsRowShown="0" headerRowDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="A3:O29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="DESCRIÇÃO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="VALOR ORÇADO" dataCellStyle="Moeda"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="VALOR ATUALIZADO" dataDxfId="2" dataCellStyle="Moeda">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="VALOR ATUALIZADO" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="PAGO" dataCellStyle="Moeda"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="A PAGAR" dataCellStyle="Moeda"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="SALDO DE CONTRATOS" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="COMPROMETIDO" dataDxfId="18" dataCellStyle="Moeda">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="COMPROMETIDO" dataDxfId="14" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="SALDO ORÇ. NOMINAL" dataDxfId="17" dataCellStyle="Moeda">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="SALDO ORÇ. NOMINAL" dataDxfId="13" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="SALDO ORÇ. CORRIGIDO" dataDxfId="16" dataCellStyle="Moeda">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="SALDO ORÇ. CORRIGIDO" dataDxfId="12" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="PREV. FINANCEIRA" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CUSTO AO TÉRMINO" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CUSTO AO TÉRMINO" dataDxfId="11" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="DESVIO NOMINAL R$" dataDxfId="14" dataCellStyle="Moeda">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="DESVIO NOMINAL R$" dataDxfId="10" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="DESVIO NOMINAL %" dataDxfId="13" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="DESVIO NOMINAL %" dataDxfId="9" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="DESVIO CORRIGIDO R$" dataDxfId="12" dataCellStyle="Moeda">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="DESVIO CORRIGIDO R$" dataDxfId="8" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="DESVIO CORRIGIDO %" dataDxfId="11" dataCellStyle="Porcentagem">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="DESVIO CORRIGIDO %" dataDxfId="7" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1872,17 +1872,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabela6" displayName="Tabela6" ref="A3:I11" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabela6" displayName="Tabela6" ref="A3:I11" totalsRowShown="0" headerRowDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A3:I11" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ÁREA / LOCAL"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="ITEM"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="1º PRAZO" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="PRAZO ATUAL" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="DELTA" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="1º PRAZO" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="PRAZO ATUAL" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="DELTA" dataDxfId="2">
       <calculatedColumnFormula>IF(OR(C4="",D4=""),"",D4-C4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="STATUS" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="STATUS" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="RESPONSÁVEL"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="OBSERVAÇÃO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="OCULTAR"/>
@@ -2250,7 +2250,9 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+      <c r="A8" s="8" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
@@ -2276,16 +2278,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
+      <c r="B2" s="28"/>
     </row>
     <row r="3" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2320,10 +2322,10 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="28"/>
     </row>
     <row r="8" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2352,10 +2354,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="23"/>
+      <c r="B11" s="28"/>
     </row>
     <row r="12" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -2407,12 +2409,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -3600,14 +3602,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
@@ -3660,14 +3662,14 @@
         <v>104</v>
       </c>
       <c r="E4" s="13">
-        <f>IF(B4="","",WEEKNUM(B4,1))</f>
+        <f t="shared" ref="E4:E67" si="0">IF(B4="","",WEEKNUM(B4,1))</f>
         <v>1</v>
       </c>
       <c r="F4" s="13" t="str">
-        <f>IF(B4="","",TEXT(B4,"mmmm"))</f>
+        <f t="shared" ref="F4:F67" si="1">IF(B4="","",TEXT(B4,"mmmm"))</f>
         <v>janeiro</v>
       </c>
-      <c r="H4" s="39"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -3680,14 +3682,14 @@
         <v>104</v>
       </c>
       <c r="E5" s="13">
-        <f>IF(B5="","",WEEKNUM(B5,1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F5" s="13" t="str">
-        <f>IF(B5="","",TEXT(B5,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
-      <c r="H5" s="39"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -3700,11 +3702,11 @@
         <v>104</v>
       </c>
       <c r="E6" s="13">
-        <f>IF(B6="","",WEEKNUM(B6,1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F6" s="13" t="str">
-        <f>IF(B6="","",TEXT(B6,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3719,11 +3721,11 @@
         <v>105</v>
       </c>
       <c r="E7" s="13">
-        <f>IF(B7="","",WEEKNUM(B7,1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F7" s="13" t="str">
-        <f>IF(B7="","",TEXT(B7,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3738,11 +3740,11 @@
         <v>105</v>
       </c>
       <c r="E8" s="13">
-        <f>IF(B8="","",WEEKNUM(B8,1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F8" s="13" t="str">
-        <f>IF(B8="","",TEXT(B8,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3760,11 +3762,11 @@
         <v>103</v>
       </c>
       <c r="E9" s="13">
-        <f>IF(B9="","",WEEKNUM(B9,1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F9" s="13" t="str">
-        <f>IF(B9="","",TEXT(B9,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3779,11 +3781,11 @@
         <v>105</v>
       </c>
       <c r="E10" s="13">
-        <f>IF(B10="","",WEEKNUM(B10,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F10" s="13" t="str">
-        <f>IF(B10="","",TEXT(B10,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3798,11 +3800,11 @@
         <v>105</v>
       </c>
       <c r="E11" s="13">
-        <f>IF(B11="","",WEEKNUM(B11,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F11" s="13" t="str">
-        <f>IF(B11="","",TEXT(B11,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3820,11 +3822,11 @@
         <v>106</v>
       </c>
       <c r="E12" s="13">
-        <f>IF(B12="","",WEEKNUM(B12,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F12" s="13" t="str">
-        <f>IF(B12="","",TEXT(B12,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3839,11 +3841,11 @@
         <v>105</v>
       </c>
       <c r="E13" s="13">
-        <f>IF(B13="","",WEEKNUM(B13,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F13" s="13" t="str">
-        <f>IF(B13="","",TEXT(B13,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3858,11 +3860,11 @@
         <v>105</v>
       </c>
       <c r="E14" s="13">
-        <f>IF(B14="","",WEEKNUM(B14,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F14" s="13" t="str">
-        <f>IF(B14="","",TEXT(B14,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3877,11 +3879,11 @@
         <v>104</v>
       </c>
       <c r="E15" s="13">
-        <f>IF(B15="","",WEEKNUM(B15,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F15" s="13" t="str">
-        <f>IF(B15="","",TEXT(B15,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3896,11 +3898,11 @@
         <v>105</v>
       </c>
       <c r="E16" s="13">
-        <f>IF(B16="","",WEEKNUM(B16,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F16" s="13" t="str">
-        <f>IF(B16="","",TEXT(B16,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3915,11 +3917,11 @@
         <v>104</v>
       </c>
       <c r="E17" s="13">
-        <f>IF(B17="","",WEEKNUM(B17,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F17" s="13" t="str">
-        <f>IF(B17="","",TEXT(B17,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3934,11 +3936,11 @@
         <v>104</v>
       </c>
       <c r="E18" s="13">
-        <f>IF(B18="","",WEEKNUM(B18,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F18" s="13" t="str">
-        <f>IF(B18="","",TEXT(B18,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3953,11 +3955,11 @@
         <v>104</v>
       </c>
       <c r="E19" s="13">
-        <f>IF(B19="","",WEEKNUM(B19,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F19" s="13" t="str">
-        <f>IF(B19="","",TEXT(B19,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3972,11 +3974,11 @@
         <v>105</v>
       </c>
       <c r="E20" s="13">
-        <f>IF(B20="","",WEEKNUM(B20,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F20" s="13" t="str">
-        <f>IF(B20="","",TEXT(B20,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -3991,11 +3993,11 @@
         <v>104</v>
       </c>
       <c r="E21" s="13">
-        <f>IF(B21="","",WEEKNUM(B21,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F21" s="13" t="str">
-        <f>IF(B21="","",TEXT(B21,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4010,11 +4012,11 @@
         <v>104</v>
       </c>
       <c r="E22" s="13">
-        <f>IF(B22="","",WEEKNUM(B22,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F22" s="13" t="str">
-        <f>IF(B22="","",TEXT(B22,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4029,11 +4031,11 @@
         <v>104</v>
       </c>
       <c r="E23" s="13">
-        <f>IF(B23="","",WEEKNUM(B23,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F23" s="13" t="str">
-        <f>IF(B23="","",TEXT(B23,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4048,11 +4050,11 @@
         <v>104</v>
       </c>
       <c r="E24" s="13">
-        <f>IF(B24="","",WEEKNUM(B24,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F24" s="13" t="str">
-        <f>IF(B24="","",TEXT(B24,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4067,11 +4069,11 @@
         <v>104</v>
       </c>
       <c r="E25" s="13">
-        <f>IF(B25="","",WEEKNUM(B25,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F25" s="13" t="str">
-        <f>IF(B25="","",TEXT(B25,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4086,11 +4088,11 @@
         <v>104</v>
       </c>
       <c r="E26" s="13">
-        <f>IF(B26="","",WEEKNUM(B26,1))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F26" s="13" t="str">
-        <f>IF(B26="","",TEXT(B26,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4105,11 +4107,11 @@
         <v>105</v>
       </c>
       <c r="E27" s="13">
-        <f>IF(B27="","",WEEKNUM(B27,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F27" s="13" t="str">
-        <f>IF(B27="","",TEXT(B27,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4124,11 +4126,11 @@
         <v>104</v>
       </c>
       <c r="E28" s="13">
-        <f>IF(B28="","",WEEKNUM(B28,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F28" s="13" t="str">
-        <f>IF(B28="","",TEXT(B28,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4143,11 +4145,11 @@
         <v>105</v>
       </c>
       <c r="E29" s="13">
-        <f>IF(B29="","",WEEKNUM(B29,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F29" s="13" t="str">
-        <f>IF(B29="","",TEXT(B29,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4165,11 +4167,11 @@
         <v>103</v>
       </c>
       <c r="E30" s="13">
-        <f>IF(B30="","",WEEKNUM(B30,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F30" s="13" t="str">
-        <f>IF(B30="","",TEXT(B30,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4184,11 +4186,11 @@
         <v>104</v>
       </c>
       <c r="E31" s="13">
-        <f>IF(B31="","",WEEKNUM(B31,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F31" s="13" t="str">
-        <f>IF(B31="","",TEXT(B31,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4203,11 +4205,11 @@
         <v>105</v>
       </c>
       <c r="E32" s="13">
-        <f>IF(B32="","",WEEKNUM(B32,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F32" s="13" t="str">
-        <f>IF(B32="","",TEXT(B32,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4222,11 +4224,11 @@
         <v>104</v>
       </c>
       <c r="E33" s="13">
-        <f>IF(B33="","",WEEKNUM(B33,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F33" s="13" t="str">
-        <f>IF(B33="","",TEXT(B33,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4241,11 +4243,11 @@
         <v>104</v>
       </c>
       <c r="E34" s="13">
-        <f>IF(B34="","",WEEKNUM(B34,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F34" s="13" t="str">
-        <f>IF(B34="","",TEXT(B34,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4260,11 +4262,11 @@
         <v>105</v>
       </c>
       <c r="E35" s="13">
-        <f>IF(B35="","",WEEKNUM(B35,1))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F35" s="13" t="str">
-        <f>IF(B35="","",TEXT(B35,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4279,11 +4281,11 @@
         <v>104</v>
       </c>
       <c r="E36" s="13">
-        <f>IF(B36="","",WEEKNUM(B36,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F36" s="13" t="str">
-        <f>IF(B36="","",TEXT(B36,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4301,11 +4303,11 @@
         <v>103</v>
       </c>
       <c r="E37" s="13">
-        <f>IF(B37="","",WEEKNUM(B37,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F37" s="13" t="str">
-        <f>IF(B37="","",TEXT(B37,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4320,11 +4322,11 @@
         <v>104</v>
       </c>
       <c r="E38" s="13">
-        <f>IF(B38="","",WEEKNUM(B38,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F38" s="13" t="str">
-        <f>IF(B38="","",TEXT(B38,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4339,11 +4341,11 @@
         <v>105</v>
       </c>
       <c r="E39" s="13">
-        <f>IF(B39="","",WEEKNUM(B39,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F39" s="13" t="str">
-        <f>IF(B39="","",TEXT(B39,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4358,11 +4360,11 @@
         <v>104</v>
       </c>
       <c r="E40" s="13">
-        <f>IF(B40="","",WEEKNUM(B40,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F40" s="13" t="str">
-        <f>IF(B40="","",TEXT(B40,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4377,11 +4379,11 @@
         <v>104</v>
       </c>
       <c r="E41" s="13">
-        <f>IF(B41="","",WEEKNUM(B41,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F41" s="13" t="str">
-        <f>IF(B41="","",TEXT(B41,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4396,11 +4398,11 @@
         <v>105</v>
       </c>
       <c r="E42" s="13">
-        <f>IF(B42="","",WEEKNUM(B42,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F42" s="13" t="str">
-        <f>IF(B42="","",TEXT(B42,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4418,11 +4420,11 @@
         <v>106</v>
       </c>
       <c r="E43" s="13">
-        <f>IF(B43="","",WEEKNUM(B43,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F43" s="13" t="str">
-        <f>IF(B43="","",TEXT(B43,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4437,11 +4439,11 @@
         <v>105</v>
       </c>
       <c r="E44" s="13">
-        <f>IF(B44="","",WEEKNUM(B44,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F44" s="13" t="str">
-        <f>IF(B44="","",TEXT(B44,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4456,11 +4458,11 @@
         <v>104</v>
       </c>
       <c r="E45" s="13">
-        <f>IF(B45="","",WEEKNUM(B45,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F45" s="13" t="str">
-        <f>IF(B45="","",TEXT(B45,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4478,11 +4480,11 @@
         <v>103</v>
       </c>
       <c r="E46" s="13">
-        <f>IF(B46="","",WEEKNUM(B46,1))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F46" s="13" t="str">
-        <f>IF(B46="","",TEXT(B46,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4497,11 +4499,11 @@
         <v>105</v>
       </c>
       <c r="E47" s="13">
-        <f>IF(B47="","",WEEKNUM(B47,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F47" s="13" t="str">
-        <f>IF(B47="","",TEXT(B47,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4516,11 +4518,11 @@
         <v>105</v>
       </c>
       <c r="E48" s="13">
-        <f>IF(B48="","",WEEKNUM(B48,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F48" s="13" t="str">
-        <f>IF(B48="","",TEXT(B48,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4538,11 +4540,11 @@
         <v>103</v>
       </c>
       <c r="E49" s="13">
-        <f>IF(B49="","",WEEKNUM(B49,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F49" s="13" t="str">
-        <f>IF(B49="","",TEXT(B49,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4557,11 +4559,11 @@
         <v>104</v>
       </c>
       <c r="E50" s="13">
-        <f>IF(B50="","",WEEKNUM(B50,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F50" s="13" t="str">
-        <f>IF(B50="","",TEXT(B50,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4579,11 +4581,11 @@
         <v>103</v>
       </c>
       <c r="E51" s="13">
-        <f>IF(B51="","",WEEKNUM(B51,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F51" s="13" t="str">
-        <f>IF(B51="","",TEXT(B51,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4598,11 +4600,11 @@
         <v>105</v>
       </c>
       <c r="E52" s="13">
-        <f>IF(B52="","",WEEKNUM(B52,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F52" s="13" t="str">
-        <f>IF(B52="","",TEXT(B52,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4617,11 +4619,11 @@
         <v>105</v>
       </c>
       <c r="E53" s="13">
-        <f>IF(B53="","",WEEKNUM(B53,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F53" s="13" t="str">
-        <f>IF(B53="","",TEXT(B53,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4636,11 +4638,11 @@
         <v>105</v>
       </c>
       <c r="E54" s="13">
-        <f>IF(B54="","",WEEKNUM(B54,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F54" s="13" t="str">
-        <f>IF(B54="","",TEXT(B54,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4655,11 +4657,11 @@
         <v>105</v>
       </c>
       <c r="E55" s="13">
-        <f>IF(B55="","",WEEKNUM(B55,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F55" s="13" t="str">
-        <f>IF(B55="","",TEXT(B55,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4677,11 +4679,11 @@
         <v>106</v>
       </c>
       <c r="E56" s="13">
-        <f>IF(B56="","",WEEKNUM(B56,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F56" s="13" t="str">
-        <f>IF(B56="","",TEXT(B56,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4696,11 +4698,11 @@
         <v>104</v>
       </c>
       <c r="E57" s="13">
-        <f>IF(B57="","",WEEKNUM(B57,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F57" s="13" t="str">
-        <f>IF(B57="","",TEXT(B57,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4715,11 +4717,11 @@
         <v>104</v>
       </c>
       <c r="E58" s="13">
-        <f>IF(B58="","",WEEKNUM(B58,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F58" s="13" t="str">
-        <f>IF(B58="","",TEXT(B58,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4734,11 +4736,11 @@
         <v>104</v>
       </c>
       <c r="E59" s="13">
-        <f>IF(B59="","",WEEKNUM(B59,1))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F59" s="13" t="str">
-        <f>IF(B59="","",TEXT(B59,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>janeiro</v>
       </c>
     </row>
@@ -4753,11 +4755,11 @@
         <v>105</v>
       </c>
       <c r="E60" s="13">
-        <f>IF(B60="","",WEEKNUM(B60,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F60" s="13" t="str">
-        <f>IF(B60="","",TEXT(B60,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4772,11 +4774,11 @@
         <v>105</v>
       </c>
       <c r="E61" s="13">
-        <f>IF(B61="","",WEEKNUM(B61,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F61" s="13" t="str">
-        <f>IF(B61="","",TEXT(B61,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4791,11 +4793,11 @@
         <v>104</v>
       </c>
       <c r="E62" s="13">
-        <f>IF(B62="","",WEEKNUM(B62,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F62" s="13" t="str">
-        <f>IF(B62="","",TEXT(B62,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4813,11 +4815,11 @@
         <v>103</v>
       </c>
       <c r="E63" s="13">
-        <f>IF(B63="","",WEEKNUM(B63,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F63" s="13" t="str">
-        <f>IF(B63="","",TEXT(B63,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4832,11 +4834,11 @@
         <v>104</v>
       </c>
       <c r="E64" s="13">
-        <f>IF(B64="","",WEEKNUM(B64,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F64" s="13" t="str">
-        <f>IF(B64="","",TEXT(B64,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4851,11 +4853,11 @@
         <v>104</v>
       </c>
       <c r="E65" s="13">
-        <f>IF(B65="","",WEEKNUM(B65,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F65" s="13" t="str">
-        <f>IF(B65="","",TEXT(B65,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4870,11 +4872,11 @@
         <v>104</v>
       </c>
       <c r="E66" s="13">
-        <f>IF(B66="","",WEEKNUM(B66,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F66" s="13" t="str">
-        <f>IF(B66="","",TEXT(B66,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4889,11 +4891,11 @@
         <v>105</v>
       </c>
       <c r="E67" s="13">
-        <f>IF(B67="","",WEEKNUM(B67,1))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F67" s="13" t="str">
-        <f>IF(B67="","",TEXT(B67,"mmmm"))</f>
+        <f t="shared" si="1"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4908,11 +4910,11 @@
         <v>104</v>
       </c>
       <c r="E68" s="13">
-        <f>IF(B68="","",WEEKNUM(B68,1))</f>
+        <f t="shared" ref="E68:E131" si="2">IF(B68="","",WEEKNUM(B68,1))</f>
         <v>6</v>
       </c>
       <c r="F68" s="13" t="str">
-        <f>IF(B68="","",TEXT(B68,"mmmm"))</f>
+        <f t="shared" ref="F68:F131" si="3">IF(B68="","",TEXT(B68,"mmmm"))</f>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4927,11 +4929,11 @@
         <v>104</v>
       </c>
       <c r="E69" s="13">
-        <f>IF(B69="","",WEEKNUM(B69,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F69" s="13" t="str">
-        <f>IF(B69="","",TEXT(B69,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4949,11 +4951,11 @@
         <v>103</v>
       </c>
       <c r="E70" s="13">
-        <f>IF(B70="","",WEEKNUM(B70,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F70" s="13" t="str">
-        <f>IF(B70="","",TEXT(B70,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4971,11 +4973,11 @@
         <v>106</v>
       </c>
       <c r="E71" s="13">
-        <f>IF(B71="","",WEEKNUM(B71,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F71" s="13" t="str">
-        <f>IF(B71="","",TEXT(B71,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -4990,11 +4992,11 @@
         <v>104</v>
       </c>
       <c r="E72" s="13">
-        <f>IF(B72="","",WEEKNUM(B72,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F72" s="13" t="str">
-        <f>IF(B72="","",TEXT(B72,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5009,11 +5011,11 @@
         <v>104</v>
       </c>
       <c r="E73" s="13">
-        <f>IF(B73="","",WEEKNUM(B73,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F73" s="13" t="str">
-        <f>IF(B73="","",TEXT(B73,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5028,11 +5030,11 @@
         <v>104</v>
       </c>
       <c r="E74" s="13">
-        <f>IF(B74="","",WEEKNUM(B74,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F74" s="13" t="str">
-        <f>IF(B74="","",TEXT(B74,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5050,11 +5052,11 @@
         <v>106</v>
       </c>
       <c r="E75" s="13">
-        <f>IF(B75="","",WEEKNUM(B75,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F75" s="13" t="str">
-        <f>IF(B75="","",TEXT(B75,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5072,11 +5074,11 @@
         <v>106</v>
       </c>
       <c r="E76" s="13">
-        <f>IF(B76="","",WEEKNUM(B76,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F76" s="13" t="str">
-        <f>IF(B76="","",TEXT(B76,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5091,11 +5093,11 @@
         <v>104</v>
       </c>
       <c r="E77" s="13">
-        <f>IF(B77="","",WEEKNUM(B77,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F77" s="13" t="str">
-        <f>IF(B77="","",TEXT(B77,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5110,11 +5112,11 @@
         <v>104</v>
       </c>
       <c r="E78" s="13">
-        <f>IF(B78="","",WEEKNUM(B78,1))</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F78" s="13" t="str">
-        <f>IF(B78="","",TEXT(B78,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5129,11 +5131,11 @@
         <v>104</v>
       </c>
       <c r="E79" s="13">
-        <f>IF(B79="","",WEEKNUM(B79,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F79" s="13" t="str">
-        <f>IF(B79="","",TEXT(B79,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5148,11 +5150,11 @@
         <v>104</v>
       </c>
       <c r="E80" s="13">
-        <f>IF(B80="","",WEEKNUM(B80,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F80" s="13" t="str">
-        <f>IF(B80="","",TEXT(B80,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5167,11 +5169,11 @@
         <v>105</v>
       </c>
       <c r="E81" s="13">
-        <f>IF(B81="","",WEEKNUM(B81,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F81" s="13" t="str">
-        <f>IF(B81="","",TEXT(B81,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5186,11 +5188,11 @@
         <v>104</v>
       </c>
       <c r="E82" s="13">
-        <f>IF(B82="","",WEEKNUM(B82,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F82" s="13" t="str">
-        <f>IF(B82="","",TEXT(B82,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5205,11 +5207,11 @@
         <v>105</v>
       </c>
       <c r="E83" s="13">
-        <f>IF(B83="","",WEEKNUM(B83,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F83" s="13" t="str">
-        <f>IF(B83="","",TEXT(B83,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5224,11 +5226,11 @@
         <v>104</v>
       </c>
       <c r="E84" s="13">
-        <f>IF(B84="","",WEEKNUM(B84,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F84" s="13" t="str">
-        <f>IF(B84="","",TEXT(B84,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5243,11 +5245,11 @@
         <v>105</v>
       </c>
       <c r="E85" s="13">
-        <f>IF(B85="","",WEEKNUM(B85,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F85" s="13" t="str">
-        <f>IF(B85="","",TEXT(B85,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5262,11 +5264,11 @@
         <v>105</v>
       </c>
       <c r="E86" s="13">
-        <f>IF(B86="","",WEEKNUM(B86,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F86" s="13" t="str">
-        <f>IF(B86="","",TEXT(B86,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5281,11 +5283,11 @@
         <v>105</v>
       </c>
       <c r="E87" s="13">
-        <f>IF(B87="","",WEEKNUM(B87,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F87" s="13" t="str">
-        <f>IF(B87="","",TEXT(B87,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5300,11 +5302,11 @@
         <v>104</v>
       </c>
       <c r="E88" s="13">
-        <f>IF(B88="","",WEEKNUM(B88,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F88" s="13" t="str">
-        <f>IF(B88="","",TEXT(B88,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5319,11 +5321,11 @@
         <v>105</v>
       </c>
       <c r="E89" s="13">
-        <f>IF(B89="","",WEEKNUM(B89,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F89" s="13" t="str">
-        <f>IF(B89="","",TEXT(B89,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5338,11 +5340,11 @@
         <v>105</v>
       </c>
       <c r="E90" s="13">
-        <f>IF(B90="","",WEEKNUM(B90,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F90" s="13" t="str">
-        <f>IF(B90="","",TEXT(B90,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5357,11 +5359,11 @@
         <v>104</v>
       </c>
       <c r="E91" s="13">
-        <f>IF(B91="","",WEEKNUM(B91,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F91" s="13" t="str">
-        <f>IF(B91="","",TEXT(B91,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5379,11 +5381,11 @@
         <v>103</v>
       </c>
       <c r="E92" s="13">
-        <f>IF(B92="","",WEEKNUM(B92,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F92" s="13" t="str">
-        <f>IF(B92="","",TEXT(B92,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5398,11 +5400,11 @@
         <v>105</v>
       </c>
       <c r="E93" s="13">
-        <f>IF(B93="","",WEEKNUM(B93,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F93" s="13" t="str">
-        <f>IF(B93="","",TEXT(B93,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5417,11 +5419,11 @@
         <v>105</v>
       </c>
       <c r="E94" s="13">
-        <f>IF(B94="","",WEEKNUM(B94,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F94" s="13" t="str">
-        <f>IF(B94="","",TEXT(B94,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5436,11 +5438,11 @@
         <v>104</v>
       </c>
       <c r="E95" s="13">
-        <f>IF(B95="","",WEEKNUM(B95,1))</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="F95" s="13" t="str">
-        <f>IF(B95="","",TEXT(B95,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5455,11 +5457,11 @@
         <v>105</v>
       </c>
       <c r="E96" s="13">
-        <f>IF(B96="","",WEEKNUM(B96,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F96" s="13" t="str">
-        <f>IF(B96="","",TEXT(B96,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5474,11 +5476,11 @@
         <v>104</v>
       </c>
       <c r="E97" s="13">
-        <f>IF(B97="","",WEEKNUM(B97,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F97" s="13" t="str">
-        <f>IF(B97="","",TEXT(B97,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5493,11 +5495,11 @@
         <v>104</v>
       </c>
       <c r="E98" s="13">
-        <f>IF(B98="","",WEEKNUM(B98,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F98" s="13" t="str">
-        <f>IF(B98="","",TEXT(B98,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5512,11 +5514,11 @@
         <v>104</v>
       </c>
       <c r="E99" s="13">
-        <f>IF(B99="","",WEEKNUM(B99,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F99" s="13" t="str">
-        <f>IF(B99="","",TEXT(B99,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5531,11 +5533,11 @@
         <v>104</v>
       </c>
       <c r="E100" s="13">
-        <f>IF(B100="","",WEEKNUM(B100,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F100" s="13" t="str">
-        <f>IF(B100="","",TEXT(B100,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5553,11 +5555,11 @@
         <v>106</v>
       </c>
       <c r="E101" s="13">
-        <f>IF(B101="","",WEEKNUM(B101,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F101" s="13" t="str">
-        <f>IF(B101="","",TEXT(B101,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5575,11 +5577,11 @@
         <v>106</v>
       </c>
       <c r="E102" s="13">
-        <f>IF(B102="","",WEEKNUM(B102,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F102" s="13" t="str">
-        <f>IF(B102="","",TEXT(B102,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5594,11 +5596,11 @@
         <v>105</v>
       </c>
       <c r="E103" s="13">
-        <f>IF(B103="","",WEEKNUM(B103,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F103" s="13" t="str">
-        <f>IF(B103="","",TEXT(B103,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5613,11 +5615,11 @@
         <v>104</v>
       </c>
       <c r="E104" s="13">
-        <f>IF(B104="","",WEEKNUM(B104,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F104" s="13" t="str">
-        <f>IF(B104="","",TEXT(B104,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5635,11 +5637,11 @@
         <v>106</v>
       </c>
       <c r="E105" s="13">
-        <f>IF(B105="","",WEEKNUM(B105,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F105" s="13" t="str">
-        <f>IF(B105="","",TEXT(B105,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5657,11 +5659,11 @@
         <v>103</v>
       </c>
       <c r="E106" s="13">
-        <f>IF(B106="","",WEEKNUM(B106,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F106" s="13" t="str">
-        <f>IF(B106="","",TEXT(B106,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5676,11 +5678,11 @@
         <v>105</v>
       </c>
       <c r="E107" s="13">
-        <f>IF(B107="","",WEEKNUM(B107,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F107" s="13" t="str">
-        <f>IF(B107="","",TEXT(B107,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5698,11 +5700,11 @@
         <v>106</v>
       </c>
       <c r="E108" s="13">
-        <f>IF(B108="","",WEEKNUM(B108,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F108" s="13" t="str">
-        <f>IF(B108="","",TEXT(B108,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5717,11 +5719,11 @@
         <v>105</v>
       </c>
       <c r="E109" s="13">
-        <f>IF(B109="","",WEEKNUM(B109,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F109" s="13" t="str">
-        <f>IF(B109="","",TEXT(B109,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5736,11 +5738,11 @@
         <v>104</v>
       </c>
       <c r="E110" s="13">
-        <f>IF(B110="","",WEEKNUM(B110,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F110" s="13" t="str">
-        <f>IF(B110="","",TEXT(B110,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5755,11 +5757,11 @@
         <v>104</v>
       </c>
       <c r="E111" s="13">
-        <f>IF(B111="","",WEEKNUM(B111,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F111" s="13" t="str">
-        <f>IF(B111="","",TEXT(B111,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5774,11 +5776,11 @@
         <v>104</v>
       </c>
       <c r="E112" s="13">
-        <f>IF(B112="","",WEEKNUM(B112,1))</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="F112" s="13" t="str">
-        <f>IF(B112="","",TEXT(B112,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5793,11 +5795,11 @@
         <v>104</v>
       </c>
       <c r="E113" s="13">
-        <f>IF(B113="","",WEEKNUM(B113,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F113" s="13" t="str">
-        <f>IF(B113="","",TEXT(B113,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5812,11 +5814,11 @@
         <v>105</v>
       </c>
       <c r="E114" s="13">
-        <f>IF(B114="","",WEEKNUM(B114,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F114" s="13" t="str">
-        <f>IF(B114="","",TEXT(B114,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5831,11 +5833,11 @@
         <v>105</v>
       </c>
       <c r="E115" s="13">
-        <f>IF(B115="","",WEEKNUM(B115,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F115" s="13" t="str">
-        <f>IF(B115="","",TEXT(B115,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5850,11 +5852,11 @@
         <v>104</v>
       </c>
       <c r="E116" s="13">
-        <f>IF(B116="","",WEEKNUM(B116,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F116" s="13" t="str">
-        <f>IF(B116="","",TEXT(B116,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5869,11 +5871,11 @@
         <v>105</v>
       </c>
       <c r="E117" s="13">
-        <f>IF(B117="","",WEEKNUM(B117,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F117" s="13" t="str">
-        <f>IF(B117="","",TEXT(B117,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5888,11 +5890,11 @@
         <v>104</v>
       </c>
       <c r="E118" s="13">
-        <f>IF(B118="","",WEEKNUM(B118,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F118" s="13" t="str">
-        <f>IF(B118="","",TEXT(B118,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5907,11 +5909,11 @@
         <v>105</v>
       </c>
       <c r="E119" s="13">
-        <f>IF(B119="","",WEEKNUM(B119,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F119" s="13" t="str">
-        <f>IF(B119="","",TEXT(B119,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5926,11 +5928,11 @@
         <v>104</v>
       </c>
       <c r="E120" s="13">
-        <f>IF(B120="","",WEEKNUM(B120,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F120" s="13" t="str">
-        <f>IF(B120="","",TEXT(B120,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5945,11 +5947,11 @@
         <v>104</v>
       </c>
       <c r="E121" s="13">
-        <f>IF(B121="","",WEEKNUM(B121,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F121" s="13" t="str">
-        <f>IF(B121="","",TEXT(B121,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5964,11 +5966,11 @@
         <v>105</v>
       </c>
       <c r="E122" s="13">
-        <f>IF(B122="","",WEEKNUM(B122,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F122" s="13" t="str">
-        <f>IF(B122="","",TEXT(B122,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -5983,11 +5985,11 @@
         <v>104</v>
       </c>
       <c r="E123" s="13">
-        <f>IF(B123="","",WEEKNUM(B123,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F123" s="13" t="str">
-        <f>IF(B123="","",TEXT(B123,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -6002,11 +6004,11 @@
         <v>104</v>
       </c>
       <c r="E124" s="13">
-        <f>IF(B124="","",WEEKNUM(B124,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F124" s="13" t="str">
-        <f>IF(B124="","",TEXT(B124,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -6021,11 +6023,11 @@
         <v>104</v>
       </c>
       <c r="E125" s="13">
-        <f>IF(B125="","",WEEKNUM(B125,1))</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F125" s="13" t="str">
-        <f>IF(B125="","",TEXT(B125,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>fevereiro</v>
       </c>
     </row>
@@ -6040,11 +6042,11 @@
         <v>105</v>
       </c>
       <c r="E126" s="13">
-        <f>IF(B126="","",WEEKNUM(B126,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F126" s="13" t="str">
-        <f>IF(B126="","",TEXT(B126,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6059,11 +6061,11 @@
         <v>105</v>
       </c>
       <c r="E127" s="13">
-        <f>IF(B127="","",WEEKNUM(B127,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F127" s="13" t="str">
-        <f>IF(B127="","",TEXT(B127,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6078,11 +6080,11 @@
         <v>104</v>
       </c>
       <c r="E128" s="13">
-        <f>IF(B128="","",WEEKNUM(B128,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F128" s="13" t="str">
-        <f>IF(B128="","",TEXT(B128,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6100,11 +6102,11 @@
         <v>106</v>
       </c>
       <c r="E129" s="13">
-        <f>IF(B129="","",WEEKNUM(B129,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F129" s="13" t="str">
-        <f>IF(B129="","",TEXT(B129,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6119,11 +6121,11 @@
         <v>105</v>
       </c>
       <c r="E130" s="13">
-        <f>IF(B130="","",WEEKNUM(B130,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F130" s="13" t="str">
-        <f>IF(B130="","",TEXT(B130,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6138,11 +6140,11 @@
         <v>105</v>
       </c>
       <c r="E131" s="13">
-        <f>IF(B131="","",WEEKNUM(B131,1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F131" s="13" t="str">
-        <f>IF(B131="","",TEXT(B131,"mmmm"))</f>
+        <f t="shared" si="3"/>
         <v>março</v>
       </c>
     </row>
@@ -6157,11 +6159,11 @@
         <v>105</v>
       </c>
       <c r="E132" s="13">
-        <f>IF(B132="","",WEEKNUM(B132,1))</f>
+        <f t="shared" ref="E132:E195" si="4">IF(B132="","",WEEKNUM(B132,1))</f>
         <v>10</v>
       </c>
       <c r="F132" s="13" t="str">
-        <f>IF(B132="","",TEXT(B132,"mmmm"))</f>
+        <f t="shared" ref="F132:F195" si="5">IF(B132="","",TEXT(B132,"mmmm"))</f>
         <v>março</v>
       </c>
     </row>
@@ -6176,11 +6178,11 @@
         <v>105</v>
       </c>
       <c r="E133" s="13">
-        <f>IF(B133="","",WEEKNUM(B133,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F133" s="13" t="str">
-        <f>IF(B133="","",TEXT(B133,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6195,11 +6197,11 @@
         <v>104</v>
       </c>
       <c r="E134" s="13">
-        <f>IF(B134="","",WEEKNUM(B134,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F134" s="13" t="str">
-        <f>IF(B134="","",TEXT(B134,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6214,11 +6216,11 @@
         <v>104</v>
       </c>
       <c r="E135" s="13">
-        <f>IF(B135="","",WEEKNUM(B135,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F135" s="13" t="str">
-        <f>IF(B135="","",TEXT(B135,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6236,11 +6238,11 @@
         <v>106</v>
       </c>
       <c r="E136" s="13">
-        <f>IF(B136="","",WEEKNUM(B136,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F136" s="13" t="str">
-        <f>IF(B136="","",TEXT(B136,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6255,11 +6257,11 @@
         <v>104</v>
       </c>
       <c r="E137" s="13">
-        <f>IF(B137="","",WEEKNUM(B137,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F137" s="13" t="str">
-        <f>IF(B137="","",TEXT(B137,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6274,11 +6276,11 @@
         <v>104</v>
       </c>
       <c r="E138" s="13">
-        <f>IF(B138="","",WEEKNUM(B138,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F138" s="13" t="str">
-        <f>IF(B138="","",TEXT(B138,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6293,11 +6295,11 @@
         <v>104</v>
       </c>
       <c r="E139" s="13">
-        <f>IF(B139="","",WEEKNUM(B139,1))</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F139" s="13" t="str">
-        <f>IF(B139="","",TEXT(B139,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6312,11 +6314,11 @@
         <v>104</v>
       </c>
       <c r="E140" s="13">
-        <f>IF(B140="","",WEEKNUM(B140,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F140" s="13" t="str">
-        <f>IF(B140="","",TEXT(B140,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6331,11 +6333,11 @@
         <v>105</v>
       </c>
       <c r="E141" s="13">
-        <f>IF(B141="","",WEEKNUM(B141,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F141" s="13" t="str">
-        <f>IF(B141="","",TEXT(B141,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6353,11 +6355,11 @@
         <v>103</v>
       </c>
       <c r="E142" s="13">
-        <f>IF(B142="","",WEEKNUM(B142,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F142" s="13" t="str">
-        <f>IF(B142="","",TEXT(B142,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6372,11 +6374,11 @@
         <v>104</v>
       </c>
       <c r="E143" s="13">
-        <f>IF(B143="","",WEEKNUM(B143,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F143" s="13" t="str">
-        <f>IF(B143="","",TEXT(B143,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6391,11 +6393,11 @@
         <v>104</v>
       </c>
       <c r="E144" s="13">
-        <f>IF(B144="","",WEEKNUM(B144,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F144" s="13" t="str">
-        <f>IF(B144="","",TEXT(B144,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6410,11 +6412,11 @@
         <v>105</v>
       </c>
       <c r="E145" s="13">
-        <f>IF(B145="","",WEEKNUM(B145,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F145" s="13" t="str">
-        <f>IF(B145="","",TEXT(B145,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6432,11 +6434,11 @@
         <v>106</v>
       </c>
       <c r="E146" s="13">
-        <f>IF(B146="","",WEEKNUM(B146,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F146" s="13" t="str">
-        <f>IF(B146="","",TEXT(B146,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6451,11 +6453,11 @@
         <v>105</v>
       </c>
       <c r="E147" s="13">
-        <f>IF(B147="","",WEEKNUM(B147,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F147" s="13" t="str">
-        <f>IF(B147="","",TEXT(B147,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6470,11 +6472,11 @@
         <v>105</v>
       </c>
       <c r="E148" s="13">
-        <f>IF(B148="","",WEEKNUM(B148,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F148" s="13" t="str">
-        <f>IF(B148="","",TEXT(B148,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6489,11 +6491,11 @@
         <v>105</v>
       </c>
       <c r="E149" s="13">
-        <f>IF(B149="","",WEEKNUM(B149,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F149" s="13" t="str">
-        <f>IF(B149="","",TEXT(B149,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6508,11 +6510,11 @@
         <v>105</v>
       </c>
       <c r="E150" s="13">
-        <f>IF(B150="","",WEEKNUM(B150,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F150" s="13" t="str">
-        <f>IF(B150="","",TEXT(B150,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6527,11 +6529,11 @@
         <v>105</v>
       </c>
       <c r="E151" s="13">
-        <f>IF(B151="","",WEEKNUM(B151,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F151" s="13" t="str">
-        <f>IF(B151="","",TEXT(B151,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6546,11 +6548,11 @@
         <v>105</v>
       </c>
       <c r="E152" s="13">
-        <f>IF(B152="","",WEEKNUM(B152,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F152" s="13" t="str">
-        <f>IF(B152="","",TEXT(B152,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6565,11 +6567,11 @@
         <v>104</v>
       </c>
       <c r="E153" s="13">
-        <f>IF(B153="","",WEEKNUM(B153,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F153" s="13" t="str">
-        <f>IF(B153="","",TEXT(B153,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6584,11 +6586,11 @@
         <v>105</v>
       </c>
       <c r="E154" s="13">
-        <f>IF(B154="","",WEEKNUM(B154,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F154" s="13" t="str">
-        <f>IF(B154="","",TEXT(B154,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6606,11 +6608,11 @@
         <v>106</v>
       </c>
       <c r="E155" s="13">
-        <f>IF(B155="","",WEEKNUM(B155,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F155" s="13" t="str">
-        <f>IF(B155="","",TEXT(B155,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6625,11 +6627,11 @@
         <v>104</v>
       </c>
       <c r="E156" s="13">
-        <f>IF(B156="","",WEEKNUM(B156,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F156" s="13" t="str">
-        <f>IF(B156="","",TEXT(B156,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6644,11 +6646,11 @@
         <v>105</v>
       </c>
       <c r="E157" s="13">
-        <f>IF(B157="","",WEEKNUM(B157,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F157" s="13" t="str">
-        <f>IF(B157="","",TEXT(B157,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6663,11 +6665,11 @@
         <v>104</v>
       </c>
       <c r="E158" s="13">
-        <f>IF(B158="","",WEEKNUM(B158,1))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F158" s="13" t="str">
-        <f>IF(B158="","",TEXT(B158,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6682,11 +6684,11 @@
         <v>105</v>
       </c>
       <c r="E159" s="13">
-        <f>IF(B159="","",WEEKNUM(B159,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F159" s="13" t="str">
-        <f>IF(B159="","",TEXT(B159,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6701,11 +6703,11 @@
         <v>104</v>
       </c>
       <c r="E160" s="13">
-        <f>IF(B160="","",WEEKNUM(B160,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F160" s="13" t="str">
-        <f>IF(B160="","",TEXT(B160,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6720,11 +6722,11 @@
         <v>105</v>
       </c>
       <c r="E161" s="13">
-        <f>IF(B161="","",WEEKNUM(B161,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F161" s="13" t="str">
-        <f>IF(B161="","",TEXT(B161,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6739,11 +6741,11 @@
         <v>105</v>
       </c>
       <c r="E162" s="13">
-        <f>IF(B162="","",WEEKNUM(B162,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F162" s="13" t="str">
-        <f>IF(B162="","",TEXT(B162,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6758,11 +6760,11 @@
         <v>105</v>
       </c>
       <c r="E163" s="13">
-        <f>IF(B163="","",WEEKNUM(B163,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F163" s="13" t="str">
-        <f>IF(B163="","",TEXT(B163,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6780,11 +6782,11 @@
         <v>103</v>
       </c>
       <c r="E164" s="13">
-        <f>IF(B164="","",WEEKNUM(B164,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F164" s="13" t="str">
-        <f>IF(B164="","",TEXT(B164,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6799,11 +6801,11 @@
         <v>104</v>
       </c>
       <c r="E165" s="13">
-        <f>IF(B165="","",WEEKNUM(B165,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F165" s="13" t="str">
-        <f>IF(B165="","",TEXT(B165,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6821,11 +6823,11 @@
         <v>103</v>
       </c>
       <c r="E166" s="13">
-        <f>IF(B166="","",WEEKNUM(B166,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F166" s="13" t="str">
-        <f>IF(B166="","",TEXT(B166,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6840,11 +6842,11 @@
         <v>104</v>
       </c>
       <c r="E167" s="13">
-        <f>IF(B167="","",WEEKNUM(B167,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F167" s="13" t="str">
-        <f>IF(B167="","",TEXT(B167,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6859,11 +6861,11 @@
         <v>105</v>
       </c>
       <c r="E168" s="13">
-        <f>IF(B168="","",WEEKNUM(B168,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F168" s="13" t="str">
-        <f>IF(B168="","",TEXT(B168,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6881,11 +6883,11 @@
         <v>106</v>
       </c>
       <c r="E169" s="13">
-        <f>IF(B169="","",WEEKNUM(B169,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F169" s="13" t="str">
-        <f>IF(B169="","",TEXT(B169,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6900,11 +6902,11 @@
         <v>105</v>
       </c>
       <c r="E170" s="13">
-        <f>IF(B170="","",WEEKNUM(B170,1))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F170" s="13" t="str">
-        <f>IF(B170="","",TEXT(B170,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6919,11 +6921,11 @@
         <v>105</v>
       </c>
       <c r="E171" s="13">
-        <f>IF(B171="","",WEEKNUM(B171,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F171" s="13" t="str">
-        <f>IF(B171="","",TEXT(B171,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6941,11 +6943,11 @@
         <v>106</v>
       </c>
       <c r="E172" s="13">
-        <f>IF(B172="","",WEEKNUM(B172,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F172" s="13" t="str">
-        <f>IF(B172="","",TEXT(B172,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6960,11 +6962,11 @@
         <v>105</v>
       </c>
       <c r="E173" s="13">
-        <f>IF(B173="","",WEEKNUM(B173,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F173" s="13" t="str">
-        <f>IF(B173="","",TEXT(B173,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -6979,11 +6981,11 @@
         <v>104</v>
       </c>
       <c r="E174" s="13">
-        <f>IF(B174="","",WEEKNUM(B174,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F174" s="13" t="str">
-        <f>IF(B174="","",TEXT(B174,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7001,11 +7003,11 @@
         <v>106</v>
       </c>
       <c r="E175" s="13">
-        <f>IF(B175="","",WEEKNUM(B175,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F175" s="13" t="str">
-        <f>IF(B175="","",TEXT(B175,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7020,11 +7022,11 @@
         <v>104</v>
       </c>
       <c r="E176" s="13">
-        <f>IF(B176="","",WEEKNUM(B176,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F176" s="13" t="str">
-        <f>IF(B176="","",TEXT(B176,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7042,11 +7044,11 @@
         <v>106</v>
       </c>
       <c r="E177" s="13">
-        <f>IF(B177="","",WEEKNUM(B177,1))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F177" s="13" t="str">
-        <f>IF(B177="","",TEXT(B177,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7061,11 +7063,11 @@
         <v>105</v>
       </c>
       <c r="E178" s="13">
-        <f>IF(B178="","",WEEKNUM(B178,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F178" s="13" t="str">
-        <f>IF(B178="","",TEXT(B178,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7080,11 +7082,11 @@
         <v>105</v>
       </c>
       <c r="E179" s="13">
-        <f>IF(B179="","",WEEKNUM(B179,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F179" s="13" t="str">
-        <f>IF(B179="","",TEXT(B179,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7099,11 +7101,11 @@
         <v>105</v>
       </c>
       <c r="E180" s="13">
-        <f>IF(B180="","",WEEKNUM(B180,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F180" s="13" t="str">
-        <f>IF(B180="","",TEXT(B180,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7118,11 +7120,11 @@
         <v>104</v>
       </c>
       <c r="E181" s="13">
-        <f>IF(B181="","",WEEKNUM(B181,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F181" s="13" t="str">
-        <f>IF(B181="","",TEXT(B181,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>março</v>
       </c>
     </row>
@@ -7140,11 +7142,11 @@
         <v>106</v>
       </c>
       <c r="E182" s="13">
-        <f>IF(B182="","",WEEKNUM(B182,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F182" s="13" t="str">
-        <f>IF(B182="","",TEXT(B182,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7159,11 +7161,11 @@
         <v>104</v>
       </c>
       <c r="E183" s="13">
-        <f>IF(B183="","",WEEKNUM(B183,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F183" s="13" t="str">
-        <f>IF(B183="","",TEXT(B183,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7178,11 +7180,11 @@
         <v>105</v>
       </c>
       <c r="E184" s="13">
-        <f>IF(B184="","",WEEKNUM(B184,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F184" s="13" t="str">
-        <f>IF(B184="","",TEXT(B184,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7197,11 +7199,11 @@
         <v>104</v>
       </c>
       <c r="E185" s="13">
-        <f>IF(B185="","",WEEKNUM(B185,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F185" s="13" t="str">
-        <f>IF(B185="","",TEXT(B185,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7219,11 +7221,11 @@
         <v>103</v>
       </c>
       <c r="E186" s="13">
-        <f>IF(B186="","",WEEKNUM(B186,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F186" s="13" t="str">
-        <f>IF(B186="","",TEXT(B186,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7238,11 +7240,11 @@
         <v>104</v>
       </c>
       <c r="E187" s="13">
-        <f>IF(B187="","",WEEKNUM(B187,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F187" s="13" t="str">
-        <f>IF(B187="","",TEXT(B187,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7260,11 +7262,11 @@
         <v>106</v>
       </c>
       <c r="E188" s="13">
-        <f>IF(B188="","",WEEKNUM(B188,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F188" s="13" t="str">
-        <f>IF(B188="","",TEXT(B188,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7279,11 +7281,11 @@
         <v>105</v>
       </c>
       <c r="E189" s="13">
-        <f>IF(B189="","",WEEKNUM(B189,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F189" s="13" t="str">
-        <f>IF(B189="","",TEXT(B189,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7298,11 +7300,11 @@
         <v>105</v>
       </c>
       <c r="E190" s="13">
-        <f>IF(B190="","",WEEKNUM(B190,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F190" s="13" t="str">
-        <f>IF(B190="","",TEXT(B190,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7317,11 +7319,11 @@
         <v>105</v>
       </c>
       <c r="E191" s="13">
-        <f>IF(B191="","",WEEKNUM(B191,1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="F191" s="13" t="str">
-        <f>IF(B191="","",TEXT(B191,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7336,11 +7338,11 @@
         <v>105</v>
       </c>
       <c r="E192" s="13">
-        <f>IF(B192="","",WEEKNUM(B192,1))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="F192" s="13" t="str">
-        <f>IF(B192="","",TEXT(B192,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7355,11 +7357,11 @@
         <v>105</v>
       </c>
       <c r="E193" s="13">
-        <f>IF(B193="","",WEEKNUM(B193,1))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="F193" s="13" t="str">
-        <f>IF(B193="","",TEXT(B193,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7374,11 +7376,11 @@
         <v>104</v>
       </c>
       <c r="E194" s="13">
-        <f>IF(B194="","",WEEKNUM(B194,1))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="F194" s="13" t="str">
-        <f>IF(B194="","",TEXT(B194,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7396,11 +7398,11 @@
         <v>106</v>
       </c>
       <c r="E195" s="13">
-        <f>IF(B195="","",WEEKNUM(B195,1))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="F195" s="13" t="str">
-        <f>IF(B195="","",TEXT(B195,"mmmm"))</f>
+        <f t="shared" si="5"/>
         <v>abril</v>
       </c>
     </row>
@@ -7415,11 +7417,11 @@
         <v>105</v>
       </c>
       <c r="E196" s="13">
-        <f>IF(B196="","",WEEKNUM(B196,1))</f>
+        <f t="shared" ref="E196:E259" si="6">IF(B196="","",WEEKNUM(B196,1))</f>
         <v>15</v>
       </c>
       <c r="F196" s="13" t="str">
-        <f>IF(B196="","",TEXT(B196,"mmmm"))</f>
+        <f t="shared" ref="F196:F259" si="7">IF(B196="","",TEXT(B196,"mmmm"))</f>
         <v>abril</v>
       </c>
     </row>
@@ -7434,11 +7436,11 @@
         <v>104</v>
       </c>
       <c r="E197" s="13">
-        <f>IF(B197="","",WEEKNUM(B197,1))</f>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="F197" s="13" t="str">
-        <f>IF(B197="","",TEXT(B197,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7456,11 +7458,11 @@
         <v>103</v>
       </c>
       <c r="E198" s="13">
-        <f>IF(B198="","",WEEKNUM(B198,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F198" s="13" t="str">
-        <f>IF(B198="","",TEXT(B198,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7475,11 +7477,11 @@
         <v>105</v>
       </c>
       <c r="E199" s="13">
-        <f>IF(B199="","",WEEKNUM(B199,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F199" s="13" t="str">
-        <f>IF(B199="","",TEXT(B199,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7494,11 +7496,11 @@
         <v>105</v>
       </c>
       <c r="E200" s="13">
-        <f>IF(B200="","",WEEKNUM(B200,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F200" s="13" t="str">
-        <f>IF(B200="","",TEXT(B200,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7513,11 +7515,11 @@
         <v>104</v>
       </c>
       <c r="E201" s="13">
-        <f>IF(B201="","",WEEKNUM(B201,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F201" s="13" t="str">
-        <f>IF(B201="","",TEXT(B201,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7532,11 +7534,11 @@
         <v>105</v>
       </c>
       <c r="E202" s="13">
-        <f>IF(B202="","",WEEKNUM(B202,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F202" s="13" t="str">
-        <f>IF(B202="","",TEXT(B202,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7551,11 +7553,11 @@
         <v>104</v>
       </c>
       <c r="E203" s="13">
-        <f>IF(B203="","",WEEKNUM(B203,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F203" s="13" t="str">
-        <f>IF(B203="","",TEXT(B203,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7570,11 +7572,11 @@
         <v>104</v>
       </c>
       <c r="E204" s="13">
-        <f>IF(B204="","",WEEKNUM(B204,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F204" s="13" t="str">
-        <f>IF(B204="","",TEXT(B204,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7589,11 +7591,11 @@
         <v>105</v>
       </c>
       <c r="E205" s="13">
-        <f>IF(B205="","",WEEKNUM(B205,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F205" s="13" t="str">
-        <f>IF(B205="","",TEXT(B205,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7608,11 +7610,11 @@
         <v>105</v>
       </c>
       <c r="E206" s="13">
-        <f>IF(B206="","",WEEKNUM(B206,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F206" s="13" t="str">
-        <f>IF(B206="","",TEXT(B206,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7627,11 +7629,11 @@
         <v>105</v>
       </c>
       <c r="E207" s="13">
-        <f>IF(B207="","",WEEKNUM(B207,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F207" s="13" t="str">
-        <f>IF(B207="","",TEXT(B207,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7646,11 +7648,11 @@
         <v>105</v>
       </c>
       <c r="E208" s="13">
-        <f>IF(B208="","",WEEKNUM(B208,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F208" s="13" t="str">
-        <f>IF(B208="","",TEXT(B208,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7668,11 +7670,11 @@
         <v>103</v>
       </c>
       <c r="E209" s="13">
-        <f>IF(B209="","",WEEKNUM(B209,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F209" s="13" t="str">
-        <f>IF(B209="","",TEXT(B209,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7687,11 +7689,11 @@
         <v>104</v>
       </c>
       <c r="E210" s="13">
-        <f>IF(B210="","",WEEKNUM(B210,1))</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F210" s="13" t="str">
-        <f>IF(B210="","",TEXT(B210,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7706,11 +7708,11 @@
         <v>105</v>
       </c>
       <c r="E211" s="13">
-        <f>IF(B211="","",WEEKNUM(B211,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F211" s="13" t="str">
-        <f>IF(B211="","",TEXT(B211,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7725,11 +7727,11 @@
         <v>105</v>
       </c>
       <c r="E212" s="13">
-        <f>IF(B212="","",WEEKNUM(B212,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F212" s="13" t="str">
-        <f>IF(B212="","",TEXT(B212,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7744,11 +7746,11 @@
         <v>104</v>
       </c>
       <c r="E213" s="13">
-        <f>IF(B213="","",WEEKNUM(B213,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F213" s="13" t="str">
-        <f>IF(B213="","",TEXT(B213,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7763,11 +7765,11 @@
         <v>105</v>
       </c>
       <c r="E214" s="13">
-        <f>IF(B214="","",WEEKNUM(B214,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F214" s="13" t="str">
-        <f>IF(B214="","",TEXT(B214,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7782,11 +7784,11 @@
         <v>105</v>
       </c>
       <c r="E215" s="13">
-        <f>IF(B215="","",WEEKNUM(B215,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F215" s="13" t="str">
-        <f>IF(B215="","",TEXT(B215,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7801,11 +7803,11 @@
         <v>104</v>
       </c>
       <c r="E216" s="13">
-        <f>IF(B216="","",WEEKNUM(B216,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F216" s="13" t="str">
-        <f>IF(B216="","",TEXT(B216,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7820,11 +7822,11 @@
         <v>104</v>
       </c>
       <c r="E217" s="13">
-        <f>IF(B217="","",WEEKNUM(B217,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F217" s="13" t="str">
-        <f>IF(B217="","",TEXT(B217,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7839,11 +7841,11 @@
         <v>105</v>
       </c>
       <c r="E218" s="13">
-        <f>IF(B218="","",WEEKNUM(B218,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F218" s="13" t="str">
-        <f>IF(B218="","",TEXT(B218,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7861,11 +7863,11 @@
         <v>103</v>
       </c>
       <c r="E219" s="13">
-        <f>IF(B219="","",WEEKNUM(B219,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F219" s="13" t="str">
-        <f>IF(B219="","",TEXT(B219,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7883,11 +7885,11 @@
         <v>103</v>
       </c>
       <c r="E220" s="13">
-        <f>IF(B220="","",WEEKNUM(B220,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F220" s="13" t="str">
-        <f>IF(B220="","",TEXT(B220,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7902,11 +7904,11 @@
         <v>104</v>
       </c>
       <c r="E221" s="13">
-        <f>IF(B221="","",WEEKNUM(B221,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F221" s="13" t="str">
-        <f>IF(B221="","",TEXT(B221,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7921,11 +7923,11 @@
         <v>105</v>
       </c>
       <c r="E222" s="13">
-        <f>IF(B222="","",WEEKNUM(B222,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F222" s="13" t="str">
-        <f>IF(B222="","",TEXT(B222,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7940,11 +7942,11 @@
         <v>105</v>
       </c>
       <c r="E223" s="13">
-        <f>IF(B223="","",WEEKNUM(B223,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F223" s="13" t="str">
-        <f>IF(B223="","",TEXT(B223,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7959,11 +7961,11 @@
         <v>104</v>
       </c>
       <c r="E224" s="13">
-        <f>IF(B224="","",WEEKNUM(B224,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F224" s="13" t="str">
-        <f>IF(B224="","",TEXT(B224,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -7981,11 +7983,11 @@
         <v>103</v>
       </c>
       <c r="E225" s="13">
-        <f>IF(B225="","",WEEKNUM(B225,1))</f>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="F225" s="13" t="str">
-        <f>IF(B225="","",TEXT(B225,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8000,11 +8002,11 @@
         <v>105</v>
       </c>
       <c r="E226" s="13">
-        <f>IF(B226="","",WEEKNUM(B226,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F226" s="13" t="str">
-        <f>IF(B226="","",TEXT(B226,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8019,11 +8021,11 @@
         <v>105</v>
       </c>
       <c r="E227" s="13">
-        <f>IF(B227="","",WEEKNUM(B227,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F227" s="13" t="str">
-        <f>IF(B227="","",TEXT(B227,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8038,11 +8040,11 @@
         <v>105</v>
       </c>
       <c r="E228" s="13">
-        <f>IF(B228="","",WEEKNUM(B228,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F228" s="13" t="str">
-        <f>IF(B228="","",TEXT(B228,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8057,11 +8059,11 @@
         <v>104</v>
       </c>
       <c r="E229" s="13">
-        <f>IF(B229="","",WEEKNUM(B229,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F229" s="13" t="str">
-        <f>IF(B229="","",TEXT(B229,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8076,11 +8078,11 @@
         <v>104</v>
       </c>
       <c r="E230" s="13">
-        <f>IF(B230="","",WEEKNUM(B230,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F230" s="13" t="str">
-        <f>IF(B230="","",TEXT(B230,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8095,11 +8097,11 @@
         <v>104</v>
       </c>
       <c r="E231" s="13">
-        <f>IF(B231="","",WEEKNUM(B231,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F231" s="13" t="str">
-        <f>IF(B231="","",TEXT(B231,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8114,11 +8116,11 @@
         <v>105</v>
       </c>
       <c r="E232" s="13">
-        <f>IF(B232="","",WEEKNUM(B232,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F232" s="13" t="str">
-        <f>IF(B232="","",TEXT(B232,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8133,11 +8135,11 @@
         <v>105</v>
       </c>
       <c r="E233" s="13">
-        <f>IF(B233="","",WEEKNUM(B233,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F233" s="13" t="str">
-        <f>IF(B233="","",TEXT(B233,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8152,11 +8154,11 @@
         <v>104</v>
       </c>
       <c r="E234" s="13">
-        <f>IF(B234="","",WEEKNUM(B234,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F234" s="13" t="str">
-        <f>IF(B234="","",TEXT(B234,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8171,11 +8173,11 @@
         <v>105</v>
       </c>
       <c r="E235" s="13">
-        <f>IF(B235="","",WEEKNUM(B235,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F235" s="13" t="str">
-        <f>IF(B235="","",TEXT(B235,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8190,11 +8192,11 @@
         <v>104</v>
       </c>
       <c r="E236" s="13">
-        <f>IF(B236="","",WEEKNUM(B236,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F236" s="13" t="str">
-        <f>IF(B236="","",TEXT(B236,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8209,11 +8211,11 @@
         <v>105</v>
       </c>
       <c r="E237" s="13">
-        <f>IF(B237="","",WEEKNUM(B237,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F237" s="13" t="str">
-        <f>IF(B237="","",TEXT(B237,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8231,11 +8233,11 @@
         <v>103</v>
       </c>
       <c r="E238" s="13">
-        <f>IF(B238="","",WEEKNUM(B238,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F238" s="13" t="str">
-        <f>IF(B238="","",TEXT(B238,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8250,11 +8252,11 @@
         <v>105</v>
       </c>
       <c r="E239" s="13">
-        <f>IF(B239="","",WEEKNUM(B239,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F239" s="13" t="str">
-        <f>IF(B239="","",TEXT(B239,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8269,11 +8271,11 @@
         <v>105</v>
       </c>
       <c r="E240" s="13">
-        <f>IF(B240="","",WEEKNUM(B240,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F240" s="13" t="str">
-        <f>IF(B240="","",TEXT(B240,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>abril</v>
       </c>
     </row>
@@ -8288,11 +8290,11 @@
         <v>105</v>
       </c>
       <c r="E241" s="13">
-        <f>IF(B241="","",WEEKNUM(B241,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F241" s="13" t="str">
-        <f>IF(B241="","",TEXT(B241,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8307,11 +8309,11 @@
         <v>105</v>
       </c>
       <c r="E242" s="13">
-        <f>IF(B242="","",WEEKNUM(B242,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F242" s="13" t="str">
-        <f>IF(B242="","",TEXT(B242,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8326,11 +8328,11 @@
         <v>104</v>
       </c>
       <c r="E243" s="13">
-        <f>IF(B243="","",WEEKNUM(B243,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F243" s="13" t="str">
-        <f>IF(B243="","",TEXT(B243,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8345,11 +8347,11 @@
         <v>104</v>
       </c>
       <c r="E244" s="13">
-        <f>IF(B244="","",WEEKNUM(B244,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F244" s="13" t="str">
-        <f>IF(B244="","",TEXT(B244,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8364,11 +8366,11 @@
         <v>104</v>
       </c>
       <c r="E245" s="13">
-        <f>IF(B245="","",WEEKNUM(B245,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F245" s="13" t="str">
-        <f>IF(B245="","",TEXT(B245,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8383,11 +8385,11 @@
         <v>105</v>
       </c>
       <c r="E246" s="13">
-        <f>IF(B246="","",WEEKNUM(B246,1))</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="F246" s="13" t="str">
-        <f>IF(B246="","",TEXT(B246,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8402,11 +8404,11 @@
         <v>104</v>
       </c>
       <c r="E247" s="13">
-        <f>IF(B247="","",WEEKNUM(B247,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F247" s="13" t="str">
-        <f>IF(B247="","",TEXT(B247,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8421,11 +8423,11 @@
         <v>104</v>
       </c>
       <c r="E248" s="13">
-        <f>IF(B248="","",WEEKNUM(B248,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F248" s="13" t="str">
-        <f>IF(B248="","",TEXT(B248,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8440,11 +8442,11 @@
         <v>104</v>
       </c>
       <c r="E249" s="13">
-        <f>IF(B249="","",WEEKNUM(B249,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F249" s="13" t="str">
-        <f>IF(B249="","",TEXT(B249,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8462,11 +8464,11 @@
         <v>106</v>
       </c>
       <c r="E250" s="13">
-        <f>IF(B250="","",WEEKNUM(B250,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F250" s="13" t="str">
-        <f>IF(B250="","",TEXT(B250,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8484,11 +8486,11 @@
         <v>103</v>
       </c>
       <c r="E251" s="13">
-        <f>IF(B251="","",WEEKNUM(B251,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F251" s="13" t="str">
-        <f>IF(B251="","",TEXT(B251,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8506,11 +8508,11 @@
         <v>106</v>
       </c>
       <c r="E252" s="13">
-        <f>IF(B252="","",WEEKNUM(B252,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F252" s="13" t="str">
-        <f>IF(B252="","",TEXT(B252,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8525,11 +8527,11 @@
         <v>105</v>
       </c>
       <c r="E253" s="13">
-        <f>IF(B253="","",WEEKNUM(B253,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F253" s="13" t="str">
-        <f>IF(B253="","",TEXT(B253,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8547,11 +8549,11 @@
         <v>106</v>
       </c>
       <c r="E254" s="13">
-        <f>IF(B254="","",WEEKNUM(B254,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F254" s="13" t="str">
-        <f>IF(B254="","",TEXT(B254,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8566,11 +8568,11 @@
         <v>105</v>
       </c>
       <c r="E255" s="13">
-        <f>IF(B255="","",WEEKNUM(B255,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F255" s="13" t="str">
-        <f>IF(B255="","",TEXT(B255,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8585,11 +8587,11 @@
         <v>105</v>
       </c>
       <c r="E256" s="13">
-        <f>IF(B256="","",WEEKNUM(B256,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F256" s="13" t="str">
-        <f>IF(B256="","",TEXT(B256,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8604,11 +8606,11 @@
         <v>105</v>
       </c>
       <c r="E257" s="13">
-        <f>IF(B257="","",WEEKNUM(B257,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F257" s="13" t="str">
-        <f>IF(B257="","",TEXT(B257,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8623,11 +8625,11 @@
         <v>105</v>
       </c>
       <c r="E258" s="13">
-        <f>IF(B258="","",WEEKNUM(B258,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F258" s="13" t="str">
-        <f>IF(B258="","",TEXT(B258,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8642,11 +8644,11 @@
         <v>104</v>
       </c>
       <c r="E259" s="13">
-        <f>IF(B259="","",WEEKNUM(B259,1))</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="F259" s="13" t="str">
-        <f>IF(B259="","",TEXT(B259,"mmmm"))</f>
+        <f t="shared" si="7"/>
         <v>maio</v>
       </c>
     </row>
@@ -8661,11 +8663,11 @@
         <v>104</v>
       </c>
       <c r="E260" s="13">
-        <f>IF(B260="","",WEEKNUM(B260,1))</f>
+        <f t="shared" ref="E260:E299" si="8">IF(B260="","",WEEKNUM(B260,1))</f>
         <v>19</v>
       </c>
       <c r="F260" s="13" t="str">
-        <f>IF(B260="","",TEXT(B260,"mmmm"))</f>
+        <f t="shared" ref="F260:F299" si="9">IF(B260="","",TEXT(B260,"mmmm"))</f>
         <v>maio</v>
       </c>
     </row>
@@ -8683,11 +8685,11 @@
         <v>103</v>
       </c>
       <c r="E261" s="13">
-        <f>IF(B261="","",WEEKNUM(B261,1))</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="F261" s="13" t="str">
-        <f>IF(B261="","",TEXT(B261,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8702,11 +8704,11 @@
         <v>104</v>
       </c>
       <c r="E262" s="13">
-        <f>IF(B262="","",WEEKNUM(B262,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F262" s="13" t="str">
-        <f>IF(B262="","",TEXT(B262,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8724,11 +8726,11 @@
         <v>103</v>
       </c>
       <c r="E263" s="13">
-        <f>IF(B263="","",WEEKNUM(B263,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F263" s="13" t="str">
-        <f>IF(B263="","",TEXT(B263,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8743,11 +8745,11 @@
         <v>105</v>
       </c>
       <c r="E264" s="13">
-        <f>IF(B264="","",WEEKNUM(B264,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F264" s="13" t="str">
-        <f>IF(B264="","",TEXT(B264,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8765,11 +8767,11 @@
         <v>106</v>
       </c>
       <c r="E265" s="13">
-        <f>IF(B265="","",WEEKNUM(B265,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F265" s="13" t="str">
-        <f>IF(B265="","",TEXT(B265,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8784,11 +8786,11 @@
         <v>104</v>
       </c>
       <c r="E266" s="13">
-        <f>IF(B266="","",WEEKNUM(B266,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F266" s="13" t="str">
-        <f>IF(B266="","",TEXT(B266,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8803,11 +8805,11 @@
         <v>104</v>
       </c>
       <c r="E267" s="13">
-        <f>IF(B267="","",WEEKNUM(B267,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F267" s="13" t="str">
-        <f>IF(B267="","",TEXT(B267,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8822,11 +8824,11 @@
         <v>104</v>
       </c>
       <c r="E268" s="13">
-        <f>IF(B268="","",WEEKNUM(B268,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F268" s="13" t="str">
-        <f>IF(B268="","",TEXT(B268,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8841,11 +8843,11 @@
         <v>105</v>
       </c>
       <c r="E269" s="13">
-        <f>IF(B269="","",WEEKNUM(B269,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F269" s="13" t="str">
-        <f>IF(B269="","",TEXT(B269,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8860,11 +8862,11 @@
         <v>104</v>
       </c>
       <c r="E270" s="13">
-        <f>IF(B270="","",WEEKNUM(B270,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F270" s="13" t="str">
-        <f>IF(B270="","",TEXT(B270,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8879,11 +8881,11 @@
         <v>105</v>
       </c>
       <c r="E271" s="13">
-        <f>IF(B271="","",WEEKNUM(B271,1))</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="F271" s="13" t="str">
-        <f>IF(B271="","",TEXT(B271,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8898,11 +8900,11 @@
         <v>105</v>
       </c>
       <c r="E272" s="13">
-        <f>IF(B272="","",WEEKNUM(B272,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F272" s="13" t="str">
-        <f>IF(B272="","",TEXT(B272,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8917,11 +8919,11 @@
         <v>104</v>
       </c>
       <c r="E273" s="13">
-        <f>IF(B273="","",WEEKNUM(B273,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F273" s="13" t="str">
-        <f>IF(B273="","",TEXT(B273,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8936,11 +8938,11 @@
         <v>104</v>
       </c>
       <c r="E274" s="13">
-        <f>IF(B274="","",WEEKNUM(B274,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F274" s="13" t="str">
-        <f>IF(B274="","",TEXT(B274,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8955,11 +8957,11 @@
         <v>105</v>
       </c>
       <c r="E275" s="13">
-        <f>IF(B275="","",WEEKNUM(B275,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F275" s="13" t="str">
-        <f>IF(B275="","",TEXT(B275,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8977,11 +8979,11 @@
         <v>103</v>
       </c>
       <c r="E276" s="13">
-        <f>IF(B276="","",WEEKNUM(B276,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F276" s="13" t="str">
-        <f>IF(B276="","",TEXT(B276,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -8996,11 +8998,11 @@
         <v>104</v>
       </c>
       <c r="E277" s="13">
-        <f>IF(B277="","",WEEKNUM(B277,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F277" s="13" t="str">
-        <f>IF(B277="","",TEXT(B277,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9015,11 +9017,11 @@
         <v>104</v>
       </c>
       <c r="E278" s="13">
-        <f>IF(B278="","",WEEKNUM(B278,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F278" s="13" t="str">
-        <f>IF(B278="","",TEXT(B278,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9034,11 +9036,11 @@
         <v>105</v>
       </c>
       <c r="E279" s="13">
-        <f>IF(B279="","",WEEKNUM(B279,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F279" s="13" t="str">
-        <f>IF(B279="","",TEXT(B279,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9053,11 +9055,11 @@
         <v>105</v>
       </c>
       <c r="E280" s="13">
-        <f>IF(B280="","",WEEKNUM(B280,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F280" s="13" t="str">
-        <f>IF(B280="","",TEXT(B280,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9072,11 +9074,11 @@
         <v>105</v>
       </c>
       <c r="E281" s="13">
-        <f>IF(B281="","",WEEKNUM(B281,1))</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="F281" s="13" t="str">
-        <f>IF(B281="","",TEXT(B281,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9091,11 +9093,11 @@
         <v>104</v>
       </c>
       <c r="E282" s="13">
-        <f>IF(B282="","",WEEKNUM(B282,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F282" s="13" t="str">
-        <f>IF(B282="","",TEXT(B282,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9110,11 +9112,11 @@
         <v>105</v>
       </c>
       <c r="E283" s="13">
-        <f>IF(B283="","",WEEKNUM(B283,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F283" s="13" t="str">
-        <f>IF(B283="","",TEXT(B283,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9129,11 +9131,11 @@
         <v>104</v>
       </c>
       <c r="E284" s="13">
-        <f>IF(B284="","",WEEKNUM(B284,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F284" s="13" t="str">
-        <f>IF(B284="","",TEXT(B284,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9148,11 +9150,11 @@
         <v>105</v>
       </c>
       <c r="E285" s="13">
-        <f>IF(B285="","",WEEKNUM(B285,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F285" s="13" t="str">
-        <f>IF(B285="","",TEXT(B285,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9167,11 +9169,11 @@
         <v>105</v>
       </c>
       <c r="E286" s="13">
-        <f>IF(B286="","",WEEKNUM(B286,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F286" s="13" t="str">
-        <f>IF(B286="","",TEXT(B286,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9186,11 +9188,11 @@
         <v>104</v>
       </c>
       <c r="E287" s="13">
-        <f>IF(B287="","",WEEKNUM(B287,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F287" s="13" t="str">
-        <f>IF(B287="","",TEXT(B287,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9208,11 +9210,11 @@
         <v>103</v>
       </c>
       <c r="E288" s="13">
-        <f>IF(B288="","",WEEKNUM(B288,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F288" s="13" t="str">
-        <f>IF(B288="","",TEXT(B288,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9227,11 +9229,11 @@
         <v>105</v>
       </c>
       <c r="E289" s="13">
-        <f>IF(B289="","",WEEKNUM(B289,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F289" s="13" t="str">
-        <f>IF(B289="","",TEXT(B289,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9246,11 +9248,11 @@
         <v>105</v>
       </c>
       <c r="E290" s="13">
-        <f>IF(B290="","",WEEKNUM(B290,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F290" s="13" t="str">
-        <f>IF(B290="","",TEXT(B290,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9268,11 +9270,11 @@
         <v>103</v>
       </c>
       <c r="E291" s="13">
-        <f>IF(B291="","",WEEKNUM(B291,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F291" s="13" t="str">
-        <f>IF(B291="","",TEXT(B291,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9287,11 +9289,11 @@
         <v>104</v>
       </c>
       <c r="E292" s="13">
-        <f>IF(B292="","",WEEKNUM(B292,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F292" s="13" t="str">
-        <f>IF(B292="","",TEXT(B292,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9306,11 +9308,11 @@
         <v>104</v>
       </c>
       <c r="E293" s="13">
-        <f>IF(B293="","",WEEKNUM(B293,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F293" s="13" t="str">
-        <f>IF(B293="","",TEXT(B293,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9325,11 +9327,11 @@
         <v>105</v>
       </c>
       <c r="E294" s="13">
-        <f>IF(B294="","",WEEKNUM(B294,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F294" s="13" t="str">
-        <f>IF(B294="","",TEXT(B294,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9344,11 +9346,11 @@
         <v>104</v>
       </c>
       <c r="E295" s="13">
-        <f>IF(B295="","",WEEKNUM(B295,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F295" s="13" t="str">
-        <f>IF(B295="","",TEXT(B295,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9363,11 +9365,11 @@
         <v>104</v>
       </c>
       <c r="E296" s="13">
-        <f>IF(B296="","",WEEKNUM(B296,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F296" s="13" t="str">
-        <f>IF(B296="","",TEXT(B296,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9382,11 +9384,11 @@
         <v>105</v>
       </c>
       <c r="E297" s="13">
-        <f>IF(B297="","",WEEKNUM(B297,1))</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="F297" s="13" t="str">
-        <f>IF(B297="","",TEXT(B297,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9401,11 +9403,11 @@
         <v>104</v>
       </c>
       <c r="E298" s="13">
-        <f>IF(B298="","",WEEKNUM(B298,1))</f>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="F298" s="13" t="str">
-        <f>IF(B298="","",TEXT(B298,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>maio</v>
       </c>
     </row>
@@ -9420,11 +9422,11 @@
         <v>104</v>
       </c>
       <c r="E299" s="13">
-        <f>IF(B299="","",WEEKNUM(B299,1))</f>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="F299" s="13" t="str">
-        <f>IF(B299="","",TEXT(B299,"mmmm"))</f>
+        <f t="shared" si="9"/>
         <v>junho</v>
       </c>
     </row>
@@ -9457,17 +9459,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -9842,42 +9844,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="28"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="33"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -10490,54 +10492,54 @@
       <c r="A14" t="s">
         <v>322</v>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="23">
         <v>149310.66844054527</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>173991.7219337674</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="23">
         <v>129357.04050000002</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="23">
         <v>1068.7280000000001</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="23">
         <v>0</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>130425.76850000002</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>18884.899940545249</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>43565.953433767383</v>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="23">
         <v>1068.7279999999882</v>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>130425.76850000001</v>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>18884.899940545263</v>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>0.12648057997319281</v>
       </c>
-      <c r="N14" s="41">
+      <c r="N14" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>43565.953433767398</v>
       </c>
-      <c r="O14" s="43">
+      <c r="O14" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.25039095509584897</v>
       </c>
@@ -10546,54 +10548,54 @@
       <c r="A15" t="s">
         <v>323</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="23">
         <v>393033.41252400004</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>458001.83561421727</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="23">
         <v>291274.98100000003</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="23">
         <v>601.06420000000003</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="23">
         <v>0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>291876.04520000005</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>101157.36732399999</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>166125.79041421722</v>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="23">
         <v>601.06420000008075</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>291876.04520000011</v>
       </c>
-      <c r="L15" s="41">
+      <c r="L15" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>101157.36732399993</v>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>0.25737599934413441</v>
       </c>
-      <c r="N15" s="41">
+      <c r="N15" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>166125.79041421716</v>
       </c>
-      <c r="O15" s="43">
+      <c r="O15" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.36271861266981414</v>
       </c>
@@ -10602,54 +10604,54 @@
       <c r="A16" t="s">
         <v>324</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="23">
         <v>1807049.0035919992</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>2105754.2038857564</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="23">
         <v>1714410.4549000002</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="23">
         <v>9710.3024999999998</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="23">
         <v>0</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>1724120.7574000002</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>82928.246191998944</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>381633.4464857562</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="23">
         <v>9710.3024999999907</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>1724120.7574000002</v>
       </c>
-      <c r="L16" s="41">
+      <c r="L16" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>82928.246191998944</v>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>4.5891531456621594E-2</v>
       </c>
-      <c r="N16" s="41">
+      <c r="N16" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>381633.4464857562</v>
       </c>
-      <c r="O16" s="43">
+      <c r="O16" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.18123361491171502</v>
       </c>
@@ -10658,54 +10660,54 @@
       <c r="A17" t="s">
         <v>325</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="23">
         <v>802658.81312800013</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>935338.31493805849</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="23">
         <v>851712.79340000148</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="23">
         <v>3974.1717999999996</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="23">
         <v>0</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>855686.96520000149</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-53028.152072001365</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>79651.349738057004</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="23">
         <v>3974.1717999987304</v>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>855686.96520000021</v>
       </c>
-      <c r="L17" s="41">
+      <c r="L17" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-53028.152072000084</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-6.6065619918065588E-2</v>
       </c>
-      <c r="N17" s="41">
+      <c r="N17" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>79651.349738058285</v>
       </c>
-      <c r="O17" s="43">
+      <c r="O17" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>8.5157796345948986E-2</v>
       </c>
@@ -10714,54 +10716,54 @@
       <c r="A18" t="s">
         <v>326</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="23">
         <v>337521.22720800014</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>393313.48606548255</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="23">
         <v>397421.55419999996</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="23">
         <v>166.398</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="23">
         <v>0</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>397587.95219999994</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-60066.724991999799</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-4274.4661345173954</v>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="23">
         <v>166.3980000000447</v>
       </c>
-      <c r="K18" s="41">
+      <c r="K18" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>397587.9522</v>
       </c>
-      <c r="L18" s="41">
+      <c r="L18" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-60066.724991999858</v>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-0.1779642883171412</v>
       </c>
-      <c r="N18" s="41">
+      <c r="N18" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-4274.4661345174536</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>-1.0867835164456578E-2</v>
       </c>
@@ -10770,54 +10772,54 @@
       <c r="A19" t="s">
         <v>327</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="23">
         <v>384778.63079476438</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>448382.53846513893</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="23">
         <v>340049.67670000001</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="23">
         <v>883.82330000000002</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="23">
         <v>0</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>340933.5</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>43845.13079476438</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>107449.03846513893</v>
       </c>
-      <c r="J19" s="40">
+      <c r="J19" s="23">
         <v>883.8232999999309</v>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>340933.49999999994</v>
       </c>
-      <c r="L19" s="41">
+      <c r="L19" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>43845.130794764438</v>
       </c>
-      <c r="M19" s="42">
+      <c r="M19" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>0.11394897555563793</v>
       </c>
-      <c r="N19" s="41">
+      <c r="N19" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>107449.03846513899</v>
       </c>
-      <c r="O19" s="43">
+      <c r="O19" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.23963698236989439</v>
       </c>
@@ -10826,54 +10828,54 @@
       <c r="A20" t="s">
         <v>328</v>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="23">
         <v>2912356.4813630003</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>3393769.0077323043</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="23">
         <v>2612096.3115000003</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="23">
         <v>30468.9581</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="23">
         <v>49578.65999999996</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>2692143.9296000004</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>220212.55176299997</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>701625.0781323039</v>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="23">
         <v>54968.978099999949</v>
       </c>
-      <c r="K20" s="41">
+      <c r="K20" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>2667065.2896000003</v>
       </c>
-      <c r="L20" s="41">
+      <c r="L20" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>245291.1917630001</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>8.422430198112367E-2</v>
       </c>
-      <c r="N20" s="41">
+      <c r="N20" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>726703.71813230403</v>
       </c>
-      <c r="O20" s="43">
+      <c r="O20" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.2141288097323639</v>
       </c>
@@ -10882,54 +10884,54 @@
       <c r="A21" t="s">
         <v>329</v>
       </c>
-      <c r="B21" s="40">
+      <c r="B21" s="23">
         <v>0</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>0</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="23">
         <v>709.58429999999998</v>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="23">
         <v>295</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="23">
         <v>0</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>1004.5843</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-1004.5843</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-1004.5843</v>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="23">
         <v>295</v>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>1004.5843</v>
       </c>
-      <c r="L21" s="41">
+      <c r="L21" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-1004.5843</v>
       </c>
-      <c r="M21" s="42">
+      <c r="M21" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="41">
+      <c r="N21" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-1004.5843</v>
       </c>
-      <c r="O21" s="43">
+      <c r="O21" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0</v>
       </c>
@@ -10938,54 +10940,54 @@
       <c r="A22" t="s">
         <v>330</v>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="23">
         <v>2071176.9247519998</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>2413542.4704135056</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="23">
         <v>1860169.5292999998</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="23">
         <v>2615.1799999999998</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="23">
         <v>31575.3</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>1894360.0092999998</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>176816.91545199999</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>519182.46111350576</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="23">
         <v>9115.1800000004005</v>
       </c>
-      <c r="K22" s="41">
+      <c r="K22" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>1869284.7093000002</v>
       </c>
-      <c r="L22" s="41">
+      <c r="L22" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>201892.21545199957</v>
       </c>
-      <c r="M22" s="42">
+      <c r="M22" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>9.7477049420186007E-2</v>
       </c>
-      <c r="N22" s="41">
+      <c r="N22" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>544257.76111350534</v>
       </c>
-      <c r="O22" s="43">
+      <c r="O22" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.22550162998385487</v>
       </c>
@@ -10994,54 +10996,54 @@
       <c r="A23" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="23">
         <v>85134.830820217729</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>99207.618354799721</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="23">
         <v>104372.26000000001</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="23">
         <v>10800</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>115172.26000000001</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-30037.429179782281</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-15964.641645200289</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="23">
         <v>0</v>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>104372.26000000001</v>
       </c>
-      <c r="L23" s="41">
+      <c r="L23" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-19237.429179782281</v>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-0.22596426156535918</v>
       </c>
-      <c r="N23" s="41">
+      <c r="N23" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-5164.6416452002886</v>
       </c>
-      <c r="O23" s="43">
+      <c r="O23" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>-5.2058921792979627E-2</v>
       </c>
@@ -11050,54 +11052,54 @@
       <c r="A24" t="s">
         <v>332</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="23">
         <v>361655.94267000002</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>421437.66999335104</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="23">
         <v>343353.35209999984</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="23">
         <v>2323.4123</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="23">
         <v>0</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>345676.76439999987</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>15979.178270000149</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>75760.90559335117</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="23">
         <v>2323.4123000001418</v>
       </c>
-      <c r="K24" s="41">
+      <c r="K24" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>345676.76439999999</v>
       </c>
-      <c r="L24" s="41">
+      <c r="L24" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>15979.178270000033</v>
       </c>
-      <c r="M24" s="42">
+      <c r="M24" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>4.4183369840491031E-2</v>
       </c>
-      <c r="N24" s="41">
+      <c r="N24" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>75760.905593351054</v>
       </c>
-      <c r="O24" s="43">
+      <c r="O24" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.17976775923838589</v>
       </c>
@@ -11106,54 +11108,54 @@
       <c r="A25" t="s">
         <v>333</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="23">
         <v>261809.08861000001</v>
       </c>
-      <c r="C25" s="40">
+      <c r="C25" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>305086.13095723302</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="23">
         <v>93079.266300000003</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="23">
         <v>1256.5</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="23">
         <v>4452.68</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>98788.446300000011</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>163020.64231</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>206297.68465723301</v>
       </c>
-      <c r="J25" s="40">
+      <c r="J25" s="23">
         <v>8139.1800000000076</v>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>101218.44630000001</v>
       </c>
-      <c r="L25" s="41">
+      <c r="L25" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>160590.64231</v>
       </c>
-      <c r="M25" s="42">
+      <c r="M25" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>0.61338834019326749</v>
       </c>
-      <c r="N25" s="41">
+      <c r="N25" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>203867.68465723301</v>
       </c>
-      <c r="O25" s="43">
+      <c r="O25" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.668229932372151</v>
       </c>
@@ -11162,54 +11164,54 @@
       <c r="A26" t="s">
         <v>334</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="23">
         <v>1252022.68</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>1458982.0290039999</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="23">
         <v>1434814.0766000007</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="23">
         <v>0</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="23">
         <v>0</v>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>1434814.0766000007</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-182791.39660000079</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>24167.952403999167</v>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="23">
         <v>0</v>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>1434814.0766000007</v>
       </c>
-      <c r="L26" s="41">
+      <c r="L26" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-182791.39660000079</v>
       </c>
-      <c r="M26" s="42">
+      <c r="M26" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-0.14599687331542652</v>
       </c>
-      <c r="N26" s="41">
+      <c r="N26" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>24167.952403999167</v>
       </c>
-      <c r="O26" s="43">
+      <c r="O26" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>1.6564941804319448E-2</v>
       </c>
@@ -11218,54 +11220,54 @@
       <c r="A27" t="s">
         <v>335</v>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="23">
         <v>2757269.2399999998</v>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>3213045.8453719998</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="23">
         <v>2786896.56</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="23">
         <v>22568.38</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="23">
         <v>130000</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>2939464.94</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-182195.70000000019</v>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>273580.90537199983</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="23">
         <v>61698.81</v>
       </c>
-      <c r="K27" s="41">
+      <c r="K27" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>2848595.37</v>
       </c>
-      <c r="L27" s="41">
+      <c r="L27" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-91326.130000000354</v>
       </c>
-      <c r="M27" s="42">
+      <c r="M27" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-3.3121948584172493E-2</v>
       </c>
-      <c r="N27" s="41">
+      <c r="N27" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>364450.47537199967</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>0.11342834584727325</v>
       </c>
@@ -11274,54 +11276,54 @@
       <c r="A28" t="s">
         <v>336</v>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="23">
         <v>150000</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>174795</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="23">
         <v>41390</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="23">
         <v>0</v>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="23">
         <v>0</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>41390</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>108610</v>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>133405</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="23">
         <v>138730</v>
       </c>
-      <c r="K28" s="41">
+      <c r="K28" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>180120</v>
       </c>
-      <c r="L28" s="41">
+      <c r="L28" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-30120</v>
       </c>
-      <c r="M28" s="42">
+      <c r="M28" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-0.20080000000000001</v>
       </c>
-      <c r="N28" s="41">
+      <c r="N28" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-5325</v>
       </c>
-      <c r="O28" s="43">
+      <c r="O28" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>-3.0464258130953402E-2</v>
       </c>
@@ -11330,54 +11332,54 @@
       <c r="A29" t="s">
         <v>337</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="23">
         <v>75013.279276999994</v>
       </c>
-      <c r="C29" s="40">
+      <c r="C29" s="23">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]*1.1653</f>
         <v>87412.974341488094</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="23">
         <v>91193.069299999988</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="23">
         <v>17303.599999999999</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="23">
         <v>0</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="24">
         <f>SUM(Tabela5[[#This Row],[PAGO]:[SALDO DE CONTRATOS]])</f>
         <v>108496.66929999998</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-33483.390022999985</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[COMPROMETIDO]]</f>
         <v>-21083.694958511885</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="23">
         <v>75000</v>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="24">
         <f>Tabela5[[#This Row],[PREV. FINANCEIRA]]+Tabela5[[#This Row],[PAGO]]</f>
         <v>166193.06929999997</v>
       </c>
-      <c r="L29" s="41">
+      <c r="L29" s="24">
         <f>Tabela5[[#This Row],[VALOR ORÇADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-91179.79002299998</v>
       </c>
-      <c r="M29" s="42">
+      <c r="M29" s="25">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO NOMINAL R$]]/Tabela5[[#This Row],[VALOR ORÇADO]],0)</f>
         <v>-1.2155153181119072</v>
       </c>
-      <c r="N29" s="41">
+      <c r="N29" s="24">
         <f>Tabela5[[#This Row],[VALOR ATUALIZADO]]-Tabela5[[#This Row],[CUSTO AO TÉRMINO]]</f>
         <v>-78780.09495851188</v>
       </c>
-      <c r="O29" s="43">
+      <c r="O29" s="26">
         <f>IFERROR(Tabela5[[#This Row],[DESVIO CORRIGIDO R$]]/Tabela5[[#This Row],[VALOR ATUALIZADO]],0)</f>
         <v>-0.90124029701528119</v>
       </c>
@@ -11388,7 +11390,7 @@
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:O29">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11408,130 +11410,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="39"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="34"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="39"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="34"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="34"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="34"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="39"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="34"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="34"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="34"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="34"/>
+      <c r="A12" s="38"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="34"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="34"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="34"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="39"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="34"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="39"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="34"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="39"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="34"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="39"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="34"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="39"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
+      <c r="A20" s="40"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11560,30 +11562,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">

--- a/templates/BASE_SEMANAL_DADOS.xlsx
+++ b/templates/BASE_SEMANAL_DADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trinuscapital-my.sharepoint.com/personal/mateus_monteiro_trinusco_com_br/Documents/Área de Trabalho/TEMPORARIO/SEMANAL - ENTREGA/Relatorios/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_C7687B5054A33544D9B01B6F03B42F07F57BE01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAD0218F-49AE-4DBF-B3D1-3F75F5289E19}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_C7687B5054A33544D9B01B6F03B42F07F57BE01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{002C6BB2-7FBF-4380-B4E1-D380137729AF}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="357">
   <si>
     <t>CHECKLIST DE ÁREA COMUM</t>
   </si>
@@ -1077,6 +1077,42 @@
   </si>
   <si>
     <t>Trinus Co.</t>
+  </si>
+  <si>
+    <t>COR</t>
+  </si>
+  <si>
+    <t>#217A3C</t>
+  </si>
+  <si>
+    <t>#1A6EE8</t>
+  </si>
+  <si>
+    <t>#E2E8F0</t>
+  </si>
+  <si>
+    <t>#800000</t>
+  </si>
+  <si>
+    <t>#FFCC66</t>
+  </si>
+  <si>
+    <t>ABREV</t>
+  </si>
+  <si>
+    <t>REST.</t>
+  </si>
+  <si>
+    <t>REPROV.</t>
+  </si>
+  <si>
+    <t>APROV</t>
+  </si>
+  <si>
+    <t>LIB</t>
+  </si>
+  <si>
+    <t>EST</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1124,7 @@
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,8 +1200,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1205,6 +1253,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF217A3C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A6EE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF800000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC66"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1344,7 +1422,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1410,6 +1488,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1763,6 +1859,18 @@
       <tableStyleElement type="firstColumnStripe" dxfId="36"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCC66"/>
+      <color rgb="FF800000"/>
+      <color rgb="FFDC2626"/>
+      <color rgb="FFB91C1C"/>
+      <color rgb="FFEBF3FB"/>
+      <color rgb="FFE2E8F0"/>
+      <color rgb="FF1A6EE8"/>
+      <color rgb="FF217A3C"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2208,60 +2316,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="29"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" s="29"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2278,16 +2434,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="34"/>
     </row>
     <row r="2" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="28"/>
+      <c r="B2" s="34"/>
     </row>
     <row r="3" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2322,10 +2478,10 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="34"/>
     </row>
     <row r="8" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2354,10 +2510,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="34"/>
     </row>
     <row r="12" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -2365,7 +2521,7 @@
       </c>
       <c r="B12" s="6">
         <f>COUNTIF(Tabela2[CATEGORIA],"Aprovou Vistoria")</f>
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2383,7 +2539,7 @@
       </c>
       <c r="B14" s="7">
         <f>IF(B13=0,"",ROUND(B12/B13*100,0))</f>
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2409,12 +2565,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -2707,7 +2863,7 @@
         <v>163</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2721,7 +2877,7 @@
         <v>164</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,7 +2891,7 @@
         <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,7 +2905,7 @@
         <v>162</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2763,7 +2919,7 @@
         <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2777,7 +2933,7 @@
         <v>164</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3602,14 +3758,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
@@ -9459,17 +9615,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -9844,42 +10000,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="33"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="39"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -11410,130 +11566,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="39"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="45"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="39"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="39"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="45"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="38"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="39"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="38"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="39"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="39"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="38"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="39"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="38"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="39"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="39"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="39"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="45"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="39"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="45"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="38"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="39"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="45"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="39"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="45"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="38"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="39"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="45"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="38"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="39"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="45"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="40"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11562,30 +11718,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
